--- a/artfynd/A 23609-2026 artfynd.xlsx
+++ b/artfynd/A 23609-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133934217</v>
       </c>
       <c r="B2" t="n">
-        <v>98016</v>
+        <v>98036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133934215</v>
       </c>
       <c r="B3" t="n">
-        <v>92396</v>
+        <v>92379</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23609-2026 artfynd.xlsx
+++ b/artfynd/A 23609-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133934217</v>
       </c>
       <c r="B2" t="n">
-        <v>98036</v>
+        <v>98046</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133934215</v>
       </c>
       <c r="B3" t="n">
-        <v>92379</v>
+        <v>92389</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23609-2026 artfynd.xlsx
+++ b/artfynd/A 23609-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133934217</v>
       </c>
       <c r="B2" t="n">
-        <v>98046</v>
+        <v>98048</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133934215</v>
       </c>
       <c r="B3" t="n">
-        <v>92389</v>
+        <v>92391</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23609-2026 artfynd.xlsx
+++ b/artfynd/A 23609-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133934217</v>
       </c>
       <c r="B2" t="n">
-        <v>98048</v>
+        <v>98049</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133934215</v>
       </c>
       <c r="B3" t="n">
-        <v>92391</v>
+        <v>92392</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23609-2026 artfynd.xlsx
+++ b/artfynd/A 23609-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133934217</v>
       </c>
       <c r="B2" t="n">
-        <v>98049</v>
+        <v>98056</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>133934215</v>
       </c>
       <c r="B3" t="n">
-        <v>92392</v>
+        <v>92399</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 23609-2026 artfynd.xlsx
+++ b/artfynd/A 23609-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133934217</v>
+        <v>133934215</v>
       </c>
       <c r="B2" t="n">
-        <v>98056</v>
+        <v>92406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>613971</v>
+        <v>613834</v>
       </c>
       <c r="R2" t="n">
-        <v>6643731</v>
+        <v>6643568</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:35</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -766,6 +766,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -782,45 +802,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133934215</v>
+        <v>133934218</v>
       </c>
       <c r="B3" t="n">
-        <v>92399</v>
+        <v>106324</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>221144</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Vittinge, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>613834</v>
+        <v>613998</v>
       </c>
       <c r="R3" t="n">
-        <v>6643568</v>
+        <v>6643748</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,26 +903,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -906,6 +915,113 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133934217</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vittinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>613971</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6643731</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vittinge</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-29</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23609-2026 artfynd.xlsx
+++ b/artfynd/A 23609-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133934215</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133934218</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1022,8 +1037,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133934217</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>